--- a/import_class_cc.xlsx
+++ b/import_class_cc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d41a2cc4a867f612/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{7BD1F39E-734E-4B37-86A0-75827B1F021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253B1CB5-B535-40FC-9BBF-85886B11EF0C}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{7BD1F39E-734E-4B37-86A0-75827B1F021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C2F57F0-3919-474A-913B-CAAE3C740226}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8408364A-AB56-463C-9617-C787E94273BF}"/>
+    <workbookView xWindow="5760" yWindow="1044" windowWidth="17280" windowHeight="8880" xr2:uid="{8408364A-AB56-463C-9617-C787E94273BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="50">
-  <si>
-    <t>player</t>
-  </si>
   <si>
     <t>block_key</t>
   </si>
@@ -175,6 +172,9 @@
   </si>
   <si>
     <t>Stormers</t>
+  </si>
+  <si>
+    <t>player_name</t>
   </si>
 </sst>
 </file>
@@ -628,36 +628,36 @@
   <sheetData>
     <row r="1" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -693,19 +693,19 @@
     </row>
     <row r="3" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -742,19 +742,19 @@
     </row>
     <row r="4" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -791,19 +791,19 @@
     </row>
     <row r="5" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -840,19 +840,19 @@
     </row>
     <row r="6" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -889,19 +889,19 @@
     </row>
     <row r="7" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -938,19 +938,19 @@
     </row>
     <row r="8" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -987,19 +987,19 @@
     </row>
     <row r="9" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1036,19 +1036,19 @@
     </row>
     <row r="10" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1085,19 +1085,19 @@
     </row>
     <row r="11" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1134,19 +1134,19 @@
     </row>
     <row r="12" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -1183,19 +1183,19 @@
     </row>
     <row r="13" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -1232,19 +1232,19 @@
     </row>
     <row r="14" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="15" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1330,19 +1330,19 @@
     </row>
     <row r="16" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -1379,19 +1379,19 @@
     </row>
     <row r="17" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1428,19 +1428,19 @@
     </row>
     <row r="18" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="19" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -1526,19 +1526,19 @@
     </row>
     <row r="20" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1575,19 +1575,19 @@
     </row>
     <row r="21" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1624,19 +1624,19 @@
     </row>
     <row r="22" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="23" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1722,19 +1722,19 @@
     </row>
     <row r="24" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1771,19 +1771,19 @@
     </row>
     <row r="25" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -1820,6531 +1820,6531 @@
     </row>
     <row r="26" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29">
         <v>4</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>6</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47">
         <v>4</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48">
         <v>5</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49">
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53">
         <v>4</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>6</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57">
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59">
         <v>4</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60">
         <v>5</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61">
         <v>6</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65">
         <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66">
         <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67">
         <v>6</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69">
         <v>2</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C71">
         <v>4</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C72">
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C73">
         <v>6</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G74" s="4"/>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75">
         <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78">
         <v>5</v>
       </c>
       <c r="D78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82">
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84">
         <v>5</v>
       </c>
       <c r="D84" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85">
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89">
         <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90">
         <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91">
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95">
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C96">
         <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97">
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101">
         <v>4</v>
       </c>
       <c r="D101" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102">
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103">
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107">
         <v>4</v>
       </c>
       <c r="D107" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108">
         <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109">
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C110">
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C112">
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C113">
         <v>4</v>
       </c>
       <c r="D113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C114">
         <v>5</v>
       </c>
       <c r="D114" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C115">
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118">
         <v>3</v>
       </c>
       <c r="D118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119">
         <v>4</v>
       </c>
       <c r="D119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120">
         <v>5</v>
       </c>
       <c r="D120" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121">
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C122">
         <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124">
         <v>3</v>
       </c>
       <c r="D124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125">
         <v>4</v>
       </c>
       <c r="D125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C126">
         <v>5</v>
       </c>
       <c r="D126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127">
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C130">
         <v>3</v>
       </c>
       <c r="D130" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131">
         <v>4</v>
       </c>
       <c r="D131" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132">
         <v>5</v>
       </c>
       <c r="D132" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C133">
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B135" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C135">
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C136">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C137">
         <v>4</v>
       </c>
       <c r="D137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C138">
         <v>5</v>
       </c>
       <c r="D138" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B139" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C139">
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B140" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B141" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C141">
         <v>2</v>
       </c>
       <c r="D141" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C142">
         <v>3</v>
       </c>
       <c r="D142" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B143" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C143">
         <v>4</v>
       </c>
       <c r="D143" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C144">
         <v>5</v>
       </c>
       <c r="D144" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B145" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C145">
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B147" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C147">
         <v>2</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B148" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148">
         <v>3</v>
       </c>
       <c r="D148" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C149">
         <v>4</v>
       </c>
       <c r="D149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150">
         <v>5</v>
       </c>
       <c r="D150" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151">
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B153" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C153">
         <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C154">
         <v>3</v>
       </c>
       <c r="D154" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C155">
         <v>4</v>
       </c>
       <c r="D155" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C156">
         <v>5</v>
       </c>
       <c r="D156" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C157">
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C159">
         <v>2</v>
       </c>
       <c r="D159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C160">
         <v>3</v>
       </c>
       <c r="D160" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C161">
         <v>4</v>
       </c>
       <c r="D161" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B162" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C162">
         <v>5</v>
       </c>
       <c r="D162" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B163" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C163">
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B164" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B165" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C165">
         <v>2</v>
       </c>
       <c r="D165" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B166" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C166">
         <v>3</v>
       </c>
       <c r="D166" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B167" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C167">
         <v>4</v>
       </c>
       <c r="D167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B168" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C168">
         <v>5</v>
       </c>
       <c r="D168" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B169" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C169">
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171">
         <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172">
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173">
         <v>4</v>
       </c>
       <c r="D173" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174">
         <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175">
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C177">
         <v>2</v>
       </c>
       <c r="D177" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C178">
         <v>3</v>
       </c>
       <c r="D178" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C179">
         <v>4</v>
       </c>
       <c r="D179" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C180">
         <v>5</v>
       </c>
       <c r="D180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C181">
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C183">
         <v>2</v>
       </c>
       <c r="D183" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C184">
         <v>3</v>
       </c>
       <c r="D184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C185">
         <v>4</v>
       </c>
       <c r="D185" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C186">
         <v>5</v>
       </c>
       <c r="D186" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C187">
         <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B188" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B189" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C189">
         <v>2</v>
       </c>
       <c r="D189" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B190" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C190">
         <v>3</v>
       </c>
       <c r="D190" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B191" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C191">
         <v>4</v>
       </c>
       <c r="D191" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B192" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C192">
         <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C193">
         <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C195">
         <v>2</v>
       </c>
       <c r="D195" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C196">
         <v>3</v>
       </c>
       <c r="D196" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C197">
         <v>4</v>
       </c>
       <c r="D197" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>5</v>
       </c>
       <c r="D198" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C199">
         <v>6</v>
       </c>
       <c r="D199" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C201">
         <v>2</v>
       </c>
       <c r="D201" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C202">
         <v>3</v>
       </c>
       <c r="D202" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C203">
         <v>4</v>
       </c>
       <c r="D203" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C204">
         <v>5</v>
       </c>
       <c r="D204" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C205">
         <v>6</v>
       </c>
       <c r="D205" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C207">
         <v>2</v>
       </c>
       <c r="D207" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C208">
         <v>3</v>
       </c>
       <c r="D208" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C209">
         <v>4</v>
       </c>
       <c r="D209" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C210">
         <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C211">
         <v>6</v>
       </c>
       <c r="D211" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C213">
         <v>2</v>
       </c>
       <c r="D213" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="214" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C214">
         <v>3</v>
       </c>
       <c r="D214" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C215">
         <v>4</v>
       </c>
       <c r="D215" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C216">
         <v>5</v>
       </c>
       <c r="D216" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C217">
         <v>6</v>
       </c>
       <c r="D217" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B218" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C219">
         <v>2</v>
       </c>
       <c r="D219" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="220" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B220" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C220">
         <v>3</v>
       </c>
       <c r="D220" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C221">
         <v>4</v>
       </c>
       <c r="D221" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B222" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C222">
         <v>5</v>
       </c>
       <c r="D222" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B223" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C223">
         <v>6</v>
       </c>
       <c r="D223" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B224" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B225" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C225">
         <v>2</v>
       </c>
       <c r="D225" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B226" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C226">
         <v>3</v>
       </c>
       <c r="D226" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B227" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C227">
         <v>4</v>
       </c>
       <c r="D227" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="228" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B228" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C228">
         <v>5</v>
       </c>
       <c r="D228" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B229" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C229">
         <v>6</v>
       </c>
       <c r="D229" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B230" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B231" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C231">
         <v>2</v>
       </c>
       <c r="D231" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B232" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C232">
         <v>3</v>
       </c>
       <c r="D232" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B233" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C233">
         <v>4</v>
       </c>
       <c r="D233" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="234" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B234" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C234">
         <v>5</v>
       </c>
       <c r="D234" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="235" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B235" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C235">
         <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B236" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="237" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B237" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C237">
         <v>2</v>
       </c>
       <c r="D237" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="238" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B238" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C238">
         <v>3</v>
       </c>
       <c r="D238" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B239" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C239">
         <v>4</v>
       </c>
       <c r="D239" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B240" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C240">
         <v>5</v>
       </c>
       <c r="D240" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="241" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B241" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C241">
         <v>6</v>
       </c>
       <c r="D241" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B242" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B243" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C243">
         <v>2</v>
       </c>
       <c r="D243" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="244" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B244" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C244">
         <v>3</v>
       </c>
       <c r="D244" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B245" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C245">
         <v>4</v>
       </c>
       <c r="D245" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="246" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B246" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C246">
         <v>5</v>
       </c>
       <c r="D246" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247">
         <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="248" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B248" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="249" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B249" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C249">
         <v>2</v>
       </c>
       <c r="D249" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B250" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C250">
         <v>3</v>
       </c>
       <c r="D250" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="251" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B251" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C251">
         <v>4</v>
       </c>
       <c r="D251" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B252" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C252">
         <v>5</v>
       </c>
       <c r="D252" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="253" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B253" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C253">
         <v>6</v>
       </c>
       <c r="D253" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B254" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="255" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B255" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C255">
         <v>2</v>
       </c>
       <c r="D255" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B256" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C256">
         <v>3</v>
       </c>
       <c r="D256" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="257" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B257" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C257">
         <v>4</v>
       </c>
       <c r="D257" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="258" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B258" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C258">
         <v>5</v>
       </c>
       <c r="D258" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="259" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B259" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C259">
         <v>6</v>
       </c>
       <c r="D259" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="260" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B260" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="261" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B261" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C261">
         <v>2</v>
       </c>
       <c r="D261" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="262" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B262" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C262">
         <v>3</v>
       </c>
       <c r="D262" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B263" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C263">
         <v>4</v>
       </c>
       <c r="D263" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="264" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B264" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C264">
         <v>5</v>
       </c>
       <c r="D264" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="265" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B265" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C265">
         <v>6</v>
       </c>
       <c r="D265" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B266" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B267" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C267">
         <v>2</v>
       </c>
       <c r="D267" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="268" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B268" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C268">
         <v>3</v>
       </c>
       <c r="D268" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="269" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B269" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C269">
         <v>4</v>
       </c>
       <c r="D269" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="270" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B270" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C270">
         <v>5</v>
       </c>
       <c r="D270" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="271" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B271" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C271">
         <v>6</v>
       </c>
       <c r="D271" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="272" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B272" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="273" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B273" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C273">
         <v>2</v>
       </c>
       <c r="D273" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="274" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B274" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C274">
         <v>3</v>
       </c>
       <c r="D274" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="275" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B275" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C275">
         <v>4</v>
       </c>
       <c r="D275" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="276" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B276" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C276">
         <v>5</v>
       </c>
       <c r="D276" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="277" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B277" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C277">
         <v>6</v>
       </c>
       <c r="D277" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="278" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B278" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="279" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B279" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C279">
         <v>2</v>
       </c>
       <c r="D279" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="280" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B280" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C280">
         <v>3</v>
       </c>
       <c r="D280" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="281" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B281" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C281">
         <v>4</v>
       </c>
       <c r="D281" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="282" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B282" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C282">
         <v>5</v>
       </c>
       <c r="D282" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="283" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B283" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C283">
         <v>6</v>
       </c>
       <c r="D283" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="284" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B284" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="285" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B285" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C285">
         <v>2</v>
       </c>
       <c r="D285" t="s">
+        <v>25</v>
+      </c>
+      <c r="E285" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="286" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B286" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C286">
         <v>3</v>
       </c>
       <c r="D286" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="287" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B287" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C287">
         <v>4</v>
       </c>
       <c r="D287" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="288" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B288" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C288">
         <v>5</v>
       </c>
       <c r="D288" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="289" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B289" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C289">
         <v>6</v>
       </c>
       <c r="D289" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="290" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B290" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="291" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B291" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C291">
         <v>2</v>
       </c>
       <c r="D291" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="292" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B292" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292">
         <v>3</v>
       </c>
       <c r="D292" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="293" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B293" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C293">
         <v>4</v>
       </c>
       <c r="D293" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="294" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B294" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C294">
         <v>5</v>
       </c>
       <c r="D294" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="295" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B295" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C295">
         <v>6</v>
       </c>
       <c r="D295" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B296" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="297" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B297" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C297">
         <v>2</v>
       </c>
       <c r="D297" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="298" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B298" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C298">
         <v>3</v>
       </c>
       <c r="D298" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="299" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B299" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C299">
         <v>4</v>
       </c>
       <c r="D299" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="300" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B300" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C300">
         <v>5</v>
       </c>
       <c r="D300" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="301" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B301" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C301">
         <v>6</v>
       </c>
       <c r="D301" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="302" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="303" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B303" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C303">
         <v>2</v>
       </c>
       <c r="D303" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B304" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C304">
         <v>3</v>
       </c>
       <c r="D304" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="305" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B305" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C305">
         <v>4</v>
       </c>
       <c r="D305" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="306" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B306" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C306">
         <v>5</v>
       </c>
       <c r="D306" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="307" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B307" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C307">
         <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="308" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B308" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="309" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B309" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C309">
         <v>2</v>
       </c>
       <c r="D309" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="310" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B310" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C310">
         <v>3</v>
       </c>
       <c r="D310" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="311" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B311" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C311">
         <v>4</v>
       </c>
       <c r="D311" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="312" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B312" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C312">
         <v>5</v>
       </c>
       <c r="D312" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="313" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B313" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C313">
         <v>6</v>
       </c>
       <c r="D313" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="314" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="315" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C315">
         <v>2</v>
       </c>
       <c r="D315" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="316" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C316">
         <v>3</v>
       </c>
       <c r="D316" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="317" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C317">
         <v>4</v>
       </c>
       <c r="D317" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="318" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C318">
         <v>5</v>
       </c>
       <c r="D318" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="319" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C319">
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="320" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C320">
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="321" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C321">
         <v>2</v>
       </c>
       <c r="D321" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="322" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C322">
         <v>3</v>
       </c>
       <c r="D322" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C323">
         <v>4</v>
       </c>
       <c r="D323" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="324" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C324">
         <v>5</v>
       </c>
       <c r="D324" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="325" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C325">
         <v>6</v>
       </c>
       <c r="D325" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="326" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C327">
         <v>2</v>
       </c>
       <c r="D327" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="328" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C328">
         <v>3</v>
       </c>
       <c r="D328" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="329" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C329">
         <v>4</v>
       </c>
       <c r="D329" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="330" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C330">
         <v>5</v>
       </c>
       <c r="D330" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="331" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C331">
         <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="332" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C332">
         <v>1</v>
       </c>
       <c r="D332" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="333" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C333">
         <v>2</v>
       </c>
       <c r="D333" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="334" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C334">
         <v>3</v>
       </c>
       <c r="D334" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="335" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C335">
         <v>4</v>
       </c>
       <c r="D335" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="336" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C336">
         <v>5</v>
       </c>
       <c r="D336" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="337" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C337">
         <v>6</v>
       </c>
       <c r="D337" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="338" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B338" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C338">
         <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="339" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B339" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C339">
         <v>2</v>
       </c>
       <c r="D339" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="340" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B340" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C340">
         <v>3</v>
       </c>
       <c r="D340" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="341" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B341" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C341">
         <v>4</v>
       </c>
       <c r="D341" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B342" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C342">
         <v>5</v>
       </c>
       <c r="D342" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="343" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B343" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C343">
         <v>6</v>
       </c>
       <c r="D343" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="344" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B344" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="345" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B345" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C345">
         <v>2</v>
       </c>
       <c r="D345" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="346" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B346" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C346">
         <v>3</v>
       </c>
       <c r="D346" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="347" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B347" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C347">
         <v>4</v>
       </c>
       <c r="D347" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="348" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B348" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C348">
         <v>5</v>
       </c>
       <c r="D348" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="349" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B349" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C349">
         <v>6</v>
       </c>
       <c r="D349" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="350" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B350" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C350">
         <v>1</v>
       </c>
       <c r="D350" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="351" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B351" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C351">
         <v>2</v>
       </c>
       <c r="D351" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="352" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B352" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C352">
         <v>3</v>
       </c>
       <c r="D352" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="353" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B353" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C353">
         <v>4</v>
       </c>
       <c r="D353" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="354" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B354" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C354">
         <v>5</v>
       </c>
       <c r="D354" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="355" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B355" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C355">
         <v>6</v>
       </c>
       <c r="D355" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="356" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B356" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C356">
         <v>1</v>
       </c>
       <c r="D356" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="357" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B357" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C357">
         <v>2</v>
       </c>
       <c r="D357" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="358" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B358" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C358">
         <v>3</v>
       </c>
       <c r="D358" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="359" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B359" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C359">
         <v>4</v>
       </c>
       <c r="D359" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="360" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B360" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C360">
         <v>5</v>
       </c>
       <c r="D360" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="361" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B361" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C361">
         <v>6</v>
       </c>
       <c r="D361" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="362" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B362" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="363" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B363" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C363">
         <v>2</v>
       </c>
       <c r="D363" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="364" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B364" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C364">
         <v>3</v>
       </c>
       <c r="D364" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="365" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B365" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C365">
         <v>4</v>
       </c>
       <c r="D365" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="366" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B366" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C366">
         <v>5</v>
       </c>
       <c r="D366" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="367" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B367" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C367">
         <v>6</v>
       </c>
       <c r="D367" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="368" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B368" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C368">
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="369" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B369" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C369">
         <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="370" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B370" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C370">
         <v>3</v>
       </c>
       <c r="D370" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="371" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B371" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C371">
         <v>4</v>
       </c>
       <c r="D371" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="372" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B372" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C372">
         <v>5</v>
       </c>
       <c r="D372" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="373" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B373" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C373">
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="374" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B374" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C374">
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="375" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B375" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C375">
         <v>2</v>
       </c>
       <c r="D375" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="376" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B376" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C376">
         <v>3</v>
       </c>
       <c r="D376" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="377" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B377" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C377">
         <v>4</v>
       </c>
       <c r="D377" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="378" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B378" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C378">
         <v>5</v>
       </c>
       <c r="D378" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="379" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B379" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C379">
         <v>6</v>
       </c>
       <c r="D379" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="380" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B380" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C380">
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="381" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B381" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C381">
         <v>2</v>
       </c>
       <c r="D381" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="382" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B382" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C382">
         <v>3</v>
       </c>
       <c r="D382" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="383" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B383" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C383">
         <v>4</v>
       </c>
       <c r="D383" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="384" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B384" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C384">
         <v>5</v>
       </c>
       <c r="D384" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="385" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B385" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C385">
         <v>6</v>
       </c>
       <c r="D385" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B386" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C386">
         <v>1</v>
       </c>
       <c r="D386" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="387" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B387" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C387">
         <v>2</v>
       </c>
       <c r="D387" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="388" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B388" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C388">
         <v>3</v>
       </c>
       <c r="D388" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="389" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B389" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C389">
         <v>4</v>
       </c>
       <c r="D389" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="390" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B390" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C390">
         <v>5</v>
       </c>
       <c r="D390" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B391" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C391">
         <v>6</v>
       </c>
       <c r="D391" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="392" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B392" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C392">
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="393" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B393" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C393">
         <v>2</v>
       </c>
       <c r="D393" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="394" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B394" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C394">
         <v>3</v>
       </c>
       <c r="D394" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="395" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B395" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C395">
         <v>4</v>
       </c>
       <c r="D395" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="396" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B396" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C396">
         <v>5</v>
       </c>
       <c r="D396" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="397" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B397" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C397">
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="398" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B398" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C398">
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="399" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B399" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C399">
         <v>2</v>
       </c>
       <c r="D399" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="400" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B400" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C400">
         <v>3</v>
       </c>
       <c r="D400" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="401" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B401" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C401">
         <v>4</v>
       </c>
       <c r="D401" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="402" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B402" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C402">
         <v>5</v>
       </c>
       <c r="D402" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="403" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B403" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C403">
         <v>6</v>
       </c>
       <c r="D403" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="404" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B404" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C404">
         <v>1</v>
       </c>
       <c r="D404" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="405" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B405" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C405">
         <v>2</v>
       </c>
       <c r="D405" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="406" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B406" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C406">
         <v>3</v>
       </c>
       <c r="D406" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="407" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B407" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C407">
         <v>4</v>
       </c>
       <c r="D407" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="408" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B408" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C408">
         <v>5</v>
       </c>
       <c r="D408" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B409" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C409">
         <v>6</v>
       </c>
       <c r="D409" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
